--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.79285404011085</v>
+        <v>5.978838781518014</v>
       </c>
       <c r="D2" t="n">
-        <v>35.71785959681255</v>
+        <v>5.80415218448204</v>
       </c>
       <c r="E2" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F2" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06507378255496</v>
+        <v>4.885574489665181</v>
       </c>
       <c r="D3" t="n">
-        <v>29.06429995393511</v>
+        <v>4.722948742514456</v>
       </c>
       <c r="E3" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F3" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.74545573092565</v>
+        <v>3.046136556275418</v>
       </c>
       <c r="D4" t="n">
-        <v>17.634541047739</v>
+        <v>2.865612920257588</v>
       </c>
       <c r="E4" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F4" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.41028046472211</v>
+        <v>4.616670575517343</v>
       </c>
       <c r="D5" t="n">
-        <v>28.3000578083401</v>
+        <v>4.598759393855267</v>
       </c>
       <c r="E5" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F5" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.90067101787685</v>
+        <v>3.071359040404988</v>
       </c>
       <c r="D6" t="n">
-        <v>18.3837174699166</v>
+        <v>2.987354088861447</v>
       </c>
       <c r="E6" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F6" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.41856330454707</v>
+        <v>5.268016536988899</v>
       </c>
       <c r="D7" t="n">
-        <v>32.11120374112291</v>
+        <v>5.218070607932472</v>
       </c>
       <c r="E7" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F7" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.18438567627422</v>
+        <v>7.179962672394562</v>
       </c>
       <c r="D8" t="n">
-        <v>43.98635432542136</v>
+        <v>7.147782577880971</v>
       </c>
       <c r="E8" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F8" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.27163432623919</v>
+        <v>3.294140578013868</v>
       </c>
       <c r="D9" t="n">
-        <v>20.57719733806494</v>
+        <v>3.343794567435554</v>
       </c>
       <c r="E9" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F9" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.3830723505573</v>
+        <v>6.399749256965562</v>
       </c>
       <c r="D10" t="n">
-        <v>39.67948501565822</v>
+        <v>6.447916315044462</v>
       </c>
       <c r="E10" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F10" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.42005133627245</v>
+        <v>8.355758342144274</v>
       </c>
       <c r="D11" t="n">
-        <v>51.3212003908211</v>
+        <v>8.339695063508429</v>
       </c>
       <c r="E11" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F11" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.77313842600216</v>
+        <v>6.463134994225352</v>
       </c>
       <c r="D12" t="n">
-        <v>39.88422743823653</v>
+        <v>6.481186958713436</v>
       </c>
       <c r="E12" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F12" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>75.19235549352224</v>
+        <v>12.21875776769737</v>
       </c>
       <c r="D13" t="n">
-        <v>75.23014511075017</v>
+        <v>12.2248985804969</v>
       </c>
       <c r="E13" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F13" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>85.09486646325063</v>
+        <v>13.82791580027823</v>
       </c>
       <c r="D14" t="n">
-        <v>85.09649096388574</v>
+        <v>13.82817978163143</v>
       </c>
       <c r="E14" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F14" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>79.88893643967138</v>
+        <v>12.9819521714466</v>
       </c>
       <c r="D15" t="n">
-        <v>80.18261510520369</v>
+        <v>13.0296749545956</v>
       </c>
       <c r="E15" t="n">
-        <v>21.51588931256193</v>
+        <v>3.496332013291313</v>
       </c>
       <c r="F15" t="n">
-        <v>21.73996233906167</v>
+        <v>3.532743880097522</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
